--- a/artfynd/A 2476-2025 artfynd.xlsx
+++ b/artfynd/A 2476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>68296474</v>
       </c>
       <c r="B2" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708159.5509551852</v>
+        <v>708160</v>
       </c>
       <c r="R2" t="n">
-        <v>6376203.0008735</v>
+        <v>6376203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2017-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,6 +778,214 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>68296461</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87412</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Viklau Möllebosån, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>708129</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6376192</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-09-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-10-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson, Kerstin Gahne</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>68296466</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Viklau Möllebosån, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>708129</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6376192</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-10-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson, Kerstin Gahne</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2476-2025 artfynd.xlsx
+++ b/artfynd/A 2476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68296474</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68296461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,8 +1001,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68296466</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>